--- a/out/MLP-Mamba1_repeat_4_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_4_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.503542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.503542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.503542575915647</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.503542575915647</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.503542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.503542575915647</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7867500136927614</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003414639360823203</v>
+        <v>-0.0003217451348025352</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4394904740363528</v>
+        <v>0.4141108407685089</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8798130973412301</v>
+        <v>0.8290058003310873</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1014965121418847</v>
+        <v>-0.09563531163542903</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3376524979583856</v>
+        <v>0.3181537839982775</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.503542575915647</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3376524979583856</v>
+        <v>0.3181537839982775</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.103542575915647</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3372816047668282</v>
+        <v>0.317874030467744</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.139463935014149</v>
+        <v>0.8594633479055712</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.618478738998788</v>
+        <v>2.038512118685154</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2180236469767364</v>
+        <v>0.1644485653896632</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.103542575915647</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.91339894831006</v>
+        <v>1.50669180736866</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3818890946258914</v>
+        <v>0.288047258267752</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.503542575915647</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.459260364100212</v>
+        <v>1.91841868128348</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2091363653887807</v>
+        <v>0.1577451608387375</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.495314834926718</v>
+        <v>1.945613506873808</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.08637616780721427</v>
+        <v>0.06515124552584857</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.458711959047085</v>
+        <v>1.918004993962326</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1076177832045682</v>
+        <v>0.08117237060192903</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.587585461945422</v>
+        <v>2.015210406641441</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0647998067328663</v>
+        <v>0.04887625232955294</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.609494262867648</v>
+        <v>2.031735657840622</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.04926527313577481</v>
+        <v>0.03715998910605837</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.643197312656199</v>
+        <v>2.057157316612956</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02179015851687477</v>
+        <v>0.01643595988750051</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.503542575915647</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.637468905498106</v>
+        <v>2.052836472861554</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01728939416196004</v>
+        <v>0.0130398794981484</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.503542575915647</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.650252211070228</v>
+        <v>2.062477793758531</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.008572575822873007</v>
+        <v>0.006463827960906852</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.650094122630363</v>
+        <v>2.06235732047787</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.004981370078009033</v>
+        <v>0.003756596564098997</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.651482667500785</v>
+        <v>2.063403677172157</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002488185039004517</v>
+        <v>0.001877252882422313</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.651474563317108</v>
+        <v>2.063396333640256</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.00122822406166175</v>
+        <v>0.0009235113564492899</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.503542575915647</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.651438345488727</v>
+        <v>2.063367794713835</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0007092576944711856</v>
+        <v>0.0005356997500202434</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.651631327810877</v>
+        <v>2.06351231826208</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002338208021949941</v>
+        <v>0.0001757895792317245</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.65138801991997</v>
+        <v>2.063327754979218</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001162727219526363</v>
+        <v>8.483164589084172e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.503542575915647</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.651384361829343</v>
+        <v>2.0633237628238</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.104729551292968e-05</v>
+        <v>4.392392260217012e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.651390113921549</v>
+        <v>2.063326927982303</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.58123458105224e-05</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.103542575915647</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.651383020363089</v>
+        <v>2.063320299989562</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.536440521940679e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.651385550358631</v>
+        <v>2.063321218225707</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.103542575915647</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.651378215964488</v>
+        <v>2.063314215934886</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.103542575915647</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.65137473074418</v>
+        <v>2.063310353859789</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.651370183431994</v>
+        <v>2.063305806547604</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.651370273376644</v>
+        <v>2.063305896492254</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.651369415443059</v>
+        <v>2.063305038558669</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.651369643764094</v>
+        <v>2.063305266879704</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.651368848099883</v>
+        <v>2.063304471215492</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.651368910369256</v>
+        <v>2.063304533484866</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.651368938044533</v>
+        <v>2.063304561160142</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.651369090258556</v>
+        <v>2.063304713374166</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.651368744317594</v>
+        <v>2.063304367433204</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.651368820424606</v>
+        <v>2.063304443540216</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.651368986476267</v>
+        <v>2.063304609591877</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.651369346254867</v>
+        <v>2.063304969370477</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.103542575915647</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.651369367011325</v>
+        <v>2.063304990126935</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.651369470793613</v>
+        <v>2.063305093909223</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.651369699114648</v>
+        <v>2.063305322230258</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.651369574575902</v>
+        <v>2.063305197691512</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.651369602251179</v>
+        <v>2.063305225366789</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.503542575915647</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.651369657601733</v>
+        <v>2.063305280717342</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.651369920516863</v>
+        <v>2.063305543632473</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.651369837491033</v>
+        <v>2.063305460606642</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.651369629926456</v>
+        <v>2.063305253042066</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.651369643764094</v>
+        <v>2.063305266879704</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.651369782140479</v>
+        <v>2.063305405256089</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.65136949846889</v>
+        <v>2.0633051215845</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.651369325498409</v>
+        <v>2.063304948614019</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.651369221716121</v>
+        <v>2.063304844831731</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.651369367011325</v>
+        <v>2.063304990126935</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.651369609169998</v>
+        <v>2.063305232285608</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.651369436199517</v>
+        <v>2.063305059315127</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.651369138690291</v>
+        <v>2.0633047618059</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.651369124852652</v>
+        <v>2.063304747968262</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.651368758155232</v>
+        <v>2.063304381270842</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.651368758155232</v>
+        <v>2.063304381270842</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.651368695885859</v>
+        <v>2.063304319001469</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.651368592103571</v>
+        <v>2.063304215219181</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.65136841913309</v>
+        <v>2.0633040422487</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.651368467564824</v>
+        <v>2.063304090680434</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.651368107786225</v>
+        <v>2.063303730901834</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.651368066273309</v>
+        <v>2.063303689388919</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.651368121623863</v>
+        <v>2.063303744739473</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.651368176974417</v>
+        <v>2.063303800090027</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.651368218487332</v>
+        <v>2.063303841602942</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.651367948653382</v>
+        <v>2.063303571768992</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.651368004003936</v>
+        <v>2.063303627119546</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.65136814929914</v>
+        <v>2.06330377241475</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7867500136927614</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.651368114705044</v>
+        <v>2.063303737820654</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.651368100867406</v>
+        <v>2.063303723983015</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.651368190812056</v>
+        <v>2.063303813927665</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.65136850907774</v>
+        <v>2.06330413219335</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.9011568254762614</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.65136832918844</v>
+        <v>2.06330395230405</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.651368370701356</v>
+        <v>2.063303993816965</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.651368183893236</v>
+        <v>2.063303807008846</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.651368253081428</v>
+        <v>2.063303876197038</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.386750013692762</v>
+        <v>-1.501156825476262</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.651368052435671</v>
+        <v>2.063303675551281</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.386750013692762</v>
+        <v>1.331760215741336</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.651368093948586</v>
+        <v>2.063303717064196</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.103542575915647</v>
+        <v>1.931760215741336</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.651368121623863</v>
+        <v>2.063303744739473</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_4_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_4_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.503542575915647</v>
+        <v>0.536076603003093</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.103542575915647</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.503542575915647</v>
+        <v>0.536076603003093</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030932</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030932</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.103542575915647</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030932</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003414639360823203</v>
+        <v>-0.0001844936767758336</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4394904740363528</v>
+        <v>0.2374577333762636</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8798130973412301</v>
+        <v>0.4753648510078776</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1014965121418847</v>
+        <v>-0.05483875091647519</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3376524979583856</v>
+        <v>0.1824344887830126</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.503542575915647</v>
+        <v>0.536076603003093</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3376524979583856</v>
+        <v>0.1824344887830126</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3372816047668282</v>
+        <v>0.182242897336574</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.139463935014149</v>
+        <v>0.5886101965423082</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.618478738998788</v>
+        <v>1.360635676081652</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2180236469767364</v>
+        <v>0.1126239909492847</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.91339894831006</v>
+        <v>0.9964141750372077</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3818890946258914</v>
+        <v>0.1972713836551376</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.503542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.459260364100212</v>
+        <v>1.278388594291932</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2091363653887807</v>
+        <v>0.1080332267747053</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.495314834926718</v>
+        <v>1.29701319272464</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.08637616780721427</v>
+        <v>0.04461909916553927</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.458711959047085</v>
+        <v>1.278105305780896</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1076177832045682</v>
+        <v>0.05559205902723764</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.587585461945422</v>
+        <v>1.344677420229237</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0647998067328663</v>
+        <v>0.03347360049221104</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030932</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.609494262867648</v>
+        <v>1.355994837461008</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.04926527313577481</v>
+        <v>0.02544803700549739</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.643197312656199</v>
+        <v>1.373404804765413</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02179015851687477</v>
+        <v>0.01125513428450758</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.503542575915647</v>
+        <v>0.536076603003093</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.637468905498106</v>
+        <v>1.370444187113562</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01728939416196004</v>
+        <v>0.008928674242544784</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.503542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.650252211070228</v>
+        <v>1.37704568191311</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.008572575822873007</v>
+        <v>0.004425121546313238</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.650094122630363</v>
+        <v>1.376961594482111</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.004981370078009033</v>
+        <v>0.002572551860627773</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.651482667500785</v>
+        <v>1.377676733969181</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002488185039004517</v>
+        <v>0.001283775930313887</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.651474563317108</v>
+        <v>1.377670129356148</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.00122822406166175</v>
+        <v>0.0006302972438863562</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.651438345488727</v>
+        <v>1.377649012850462</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0007092576944711856</v>
+        <v>0.0003654794583472038</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.651631327810877</v>
+        <v>1.377746464170556</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002338208021949941</v>
+        <v>0.0001177583562684549</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.65138801991997</v>
+        <v>1.377618431473584</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001162727219526363</v>
+        <v>5.788215212358921e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.651384361829343</v>
+        <v>1.377614127278445</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.104729551292968e-05</v>
+        <v>2.924674582151908e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.536076603003093</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.651390113921549</v>
+        <v>1.377614702437366</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.58123458105224e-05</v>
+        <v>1.159126312874283e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.103542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.651383020363089</v>
+        <v>1.377608616117356</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.536440521940679e-05</v>
+        <v>3.727602236888622e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.651385550358631</v>
+        <v>1.377607382926203</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.651378215964488</v>
+        <v>1.377601048065656</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.65137473074418</v>
+        <v>1.377596805455502</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.651370183431994</v>
+        <v>1.377597033776537</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.651370273376644</v>
+        <v>1.377597123721187</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.651369415443059</v>
+        <v>1.377596265787602</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.651369643764094</v>
+        <v>1.377596494108637</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.651368848099883</v>
+        <v>1.377595698444425</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.651368910369256</v>
+        <v>1.377595760713798</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.651368938044533</v>
+        <v>1.377595788389075</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.651369090258556</v>
+        <v>1.377595940603098</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.651368744317594</v>
+        <v>1.377595594662136</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.103542575915647</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.651368820424606</v>
+        <v>1.377595670769148</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.651368986476267</v>
+        <v>1.37759583682081</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.651369346254867</v>
+        <v>1.377596196599409</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.103542575915647</v>
+        <v>1.396714909199301</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.651369367011325</v>
+        <v>1.377596217355867</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030932</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.651369470793613</v>
+        <v>1.377596321138156</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.651369699114648</v>
+        <v>1.377596549459191</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.651369574575902</v>
+        <v>1.377596424920444</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.651369602251179</v>
+        <v>1.377596452595721</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.503542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.651369657601733</v>
+        <v>1.377596507946275</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.651369920516863</v>
+        <v>1.377596770861406</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.651369837491033</v>
+        <v>1.377596687835575</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.651369629926456</v>
+        <v>1.377596480270998</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.651369643764094</v>
+        <v>1.377596494108637</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.651369782140479</v>
+        <v>1.377596632485021</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.65136949846889</v>
+        <v>1.377596348813433</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.651369325498409</v>
+        <v>1.377596175842952</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.651369221716121</v>
+        <v>1.377596072060664</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.651369367011325</v>
+        <v>1.377596217355867</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.651369609169998</v>
+        <v>1.377596459514541</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.5852000093893223</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.651369436199517</v>
+        <v>1.37759628654406</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.651369138690291</v>
+        <v>1.377595989034833</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.651369124852652</v>
+        <v>1.377595975197194</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.651368758155232</v>
+        <v>1.377595608499775</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.103542575915647</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.651368758155232</v>
+        <v>1.377595608499775</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.651368695885859</v>
+        <v>1.377595546230402</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.651368592103571</v>
+        <v>1.377595442448113</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.65136841913309</v>
+        <v>1.377595269477632</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.651368467564824</v>
+        <v>1.377595317909367</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.651368107786225</v>
+        <v>1.377594958130767</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.651368066273309</v>
+        <v>1.377594916617852</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.651368121623863</v>
+        <v>1.377594971968406</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.651368176974417</v>
+        <v>1.37759502731896</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.651368218487332</v>
+        <v>1.377595068831875</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.651367948653382</v>
+        <v>1.377594798997925</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.103542575915647</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.651368004003936</v>
+        <v>1.377594854348478</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.65136814929914</v>
+        <v>1.377594999643682</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.5852000093893223</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.651368114705044</v>
+        <v>1.377594965049586</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.386750013692762</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.651368100867406</v>
+        <v>1.377594951211948</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.651368190812056</v>
+        <v>1.377595041156598</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.103542575915647</v>
+        <v>0.7360766030030931</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.65136850907774</v>
+        <v>1.377595359422282</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7867500136927614</v>
+        <v>0.07543829680688541</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.65136832918844</v>
+        <v>1.377595179532982</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7867500136927614</v>
+        <v>-0.5852000093893223</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.651368370701356</v>
+        <v>1.377595221045898</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.651368183893236</v>
+        <v>1.377595034237779</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.651368253081428</v>
+        <v>1.377595103425971</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.7852000093893223</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.651368052435671</v>
+        <v>1.377594902780213</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.386750013692762</v>
+        <v>-0.1245617031931146</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.651368093948586</v>
+        <v>1.377594944293129</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.103542575915647</v>
+        <v>0.2057574499049892</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.651368121623863</v>
+        <v>1.377594971968406</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_4_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_4_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4969074726104736</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.02000000000000013</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4939636290073395</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.09000000000000008</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.5054330825805664</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.536076603003093</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5494598746299744</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.3993372321128845</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.5435335636138916</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4379075169563293</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7360766030030931</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.500942587852478</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.7360766030030931</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.5237912535667419</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.7360766030030931</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.3828900456428528</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4938473701477051</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.450840562582016</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.5788302421569824</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4161769449710846</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4089353084564209</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4033899903297424</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.525516152381897</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.536076603003093</v>
+        <v>0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.5329249501228333</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.396714909199301</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.5906360745429993</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.7360766030030932</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4608661234378815</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.3588783144950867</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4464789927005768</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.418624222278595</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.6220713257789612</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.3811659812927246</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.7825682163238525</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.5354462862014771</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.396714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5291942954063416</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.7360766030030932</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4157023727893829</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.5704649686813354</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4133317768573761</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3854548931121826</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4885575175285339</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.633682906627655</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4648994207382202</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4492685794830322</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.6125249862670898</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4003803730010986</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4678801894187927</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4903578758239746</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1245617031931146</v>
+        <v>0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.7288527488708496</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.8262936472892761</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.396714909199301</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.7873370051383972</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7360766030030932</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001844936767758336</v>
+        <v>-0.0001505071560592624</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2374577333762636</v>
+        <v>0.1937144337915407</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>0.3828748762607574</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4753648510078776</v>
+        <v>0.3877954684738684</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05483875091647519</v>
+        <v>-0.04473662505144678</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.1698305755853653</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1824344887830126</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.7591794729232788</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.536076603003093</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1824344887830126</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.7805696725845337</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.7360766030030931</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.182242897336574</v>
+        <v>0.1487414633451898</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.5886101965423082</v>
+        <v>0.2637136339091658</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.3799735009670258</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7360766030030931</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.360635676081652</v>
+        <v>0.6766938466458761</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1126239909492847</v>
+        <v>0.05045857031788842</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.8114120364189148</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.9964141750372077</v>
+        <v>0.5135126392995678</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1972713836551376</v>
+        <v>0.08838297130618772</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.6295160055160522</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.278388594291932</v>
+        <v>0.6398450573440544</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1080332267747053</v>
+        <v>0.0484019696582307</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4325738847255707</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.29701319272464</v>
+        <v>0.6481894091249795</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04461909916553927</v>
+        <v>0.01999052154930155</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.8586639761924744</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.278105305780896</v>
+        <v>0.639718136210965</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.05559205902723764</v>
+        <v>0.02490647437945315</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.8668186664581299</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.396714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.344677420229237</v>
+        <v>0.6695445068397418</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03347360049221104</v>
+        <v>0.01499741439236807</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.8955591917037964</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.7360766030030932</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.355994837461008</v>
+        <v>0.6746150692310582</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02544803700549739</v>
+        <v>0.01139986482293197</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.3726187646389008</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.373404804765413</v>
+        <v>0.6824140553408168</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01125513428450758</v>
+        <v>0.005039413016094149</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.8241418600082397</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.536076603003093</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.370444187113562</v>
+        <v>0.6810847644414517</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.008928674242544784</v>
+        <v>0.003997750147633703</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.7230563759803772</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.396714909199301</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.37704568191311</v>
+        <v>0.6840403328480719</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.004425121546313238</v>
+        <v>0.001981175329064207</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.9396490454673767</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.396714909199301</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.376961594482111</v>
+        <v>0.6839998845479104</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002572551860627773</v>
+        <v>0.001149952696014928</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.9601947665214539</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7360766030030931</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.377676733969181</v>
+        <v>0.6843175655596112</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001283775930313887</v>
+        <v>0.0005710217476346492</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.03837104141712189</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7360766030030931</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.377670129356148</v>
+        <v>0.6843118483736508</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0006302972438863562</v>
+        <v>0.0002795901680757886</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.9017547965049744</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.377649012850462</v>
+        <v>0.6842996096653126</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003654794583472038</v>
+        <v>0.0001618826388951368</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.02854069508612156</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.377746464170556</v>
+        <v>0.684340758908598</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001177583562684549</v>
+        <v>5.079925284929769e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.293013870716095</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.377618431473584</v>
+        <v>0.6842803381422825</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>5.788215212358921e-05</v>
+        <v>2.194949376725252e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.5208118557929993</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.377614127278445</v>
+        <v>0.6842756501820041</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.924674582151908e-05</v>
+        <v>9.677176780651038e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.2160382568836212</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.536076603003093</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.377614702437366</v>
+        <v>0.6842732401815853</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.159126312874283e-05</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.9337095618247986</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.377608616117356</v>
+        <v>0.6842676985088549</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.1359606236219406</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.7360766030030931</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.377607382926203</v>
+        <v>0.684264849936153</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.8345468044281006</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.377601048065656</v>
+        <v>0.6842591825058794</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.870108962059021</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.377596805455502</v>
+        <v>0.684259563040937</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.09057268500328064</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.16</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.377597033776537</v>
+        <v>0.6842597913619718</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.01296816952526569</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.377597123721187</v>
+        <v>0.6842598813066217</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.3566121160984039</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.377596265787602</v>
+        <v>0.6842590233730369</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.03805523365736008</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.377596494108637</v>
+        <v>0.6842592516940715</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4605409502983093</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.377595698444425</v>
+        <v>0.6842584560298598</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.2162179499864578</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.377595760713798</v>
+        <v>0.6842585182992329</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4318846464157104</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.377595788389075</v>
+        <v>0.6842585459745097</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.4644351005554199</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.377595940603098</v>
+        <v>0.684258698188533</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.2142759412527084</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.377595594662136</v>
+        <v>0.6842583522475714</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.6062389016151428</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.377595670769148</v>
+        <v>0.6842584283545829</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.2361670881509781</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.37759583682081</v>
+        <v>0.6842585944062446</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.8649059534072876</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.377596196599409</v>
+        <v>0.6842589541848446</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5488944053649902</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.396714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.377596217355867</v>
+        <v>0.6842589749413023</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.8617321848869324</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7360766030030932</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.377596321138156</v>
+        <v>0.6842590787235908</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.2353908866643906</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.377596549459191</v>
+        <v>0.6842593070446256</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.235644742846489</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.377596424920444</v>
+        <v>0.6842591825058794</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3782603740692139</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.377596452595721</v>
+        <v>0.6842592101811562</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.811101496219635</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.377596507946275</v>
+        <v>0.6842592655317101</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.0546686053276062</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.377596770861406</v>
+        <v>0.6842595284468408</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.2352587431669235</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.377596687835575</v>
+        <v>0.68425944542101</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4242333173751831</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.377596480270998</v>
+        <v>0.6842592378564333</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4028035700321198</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.377596494108637</v>
+        <v>0.6842592516940715</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.1436575204133987</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.377596632485021</v>
+        <v>0.6842593900704563</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.08840598911046982</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.377596348813433</v>
+        <v>0.6842591063988677</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.1922974437475204</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1245617031931146</v>
+        <v>0.16</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.377596175842952</v>
+        <v>0.684258933428387</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.7178521156311035</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.377596072060664</v>
+        <v>0.6842588296460984</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.6023468971252441</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.377596217355867</v>
+        <v>0.6842589749413023</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3031907975673676</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.16</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.377596459514541</v>
+        <v>0.6842592170999756</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.03906887397170067</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5852000093893223</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.37759628654406</v>
+        <v>0.6842590441294946</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3287970125675201</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.377595989034833</v>
+        <v>0.6842587466202676</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.0459986999630928</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.377595975197194</v>
+        <v>0.6842587327826291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3319389522075653</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.377595608499775</v>
+        <v>0.6842583660852098</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.6512879729270935</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1245617031931146</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.377595608499775</v>
+        <v>0.6842583660852098</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.08453602343797684</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.377595546230402</v>
+        <v>0.6842583038158367</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.2063437700271606</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.377595442448113</v>
+        <v>0.6842582000335483</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3348000347614288</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.377595269477632</v>
+        <v>0.6842580270630675</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.1126058846712112</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.377595317909367</v>
+        <v>0.6842580754948021</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.1785107105970383</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.377594958130767</v>
+        <v>0.6842577157162021</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4637946784496307</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.377594916617852</v>
+        <v>0.6842576742032866</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4768587946891785</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.377594971968406</v>
+        <v>0.6842577295538403</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.2677534818649292</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.37759502731896</v>
+        <v>0.6842577849043943</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.1710337549448013</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7852000093893223</v>
+        <v>0.16</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.377595068831875</v>
+        <v>0.6842578264173097</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.2430217117071152</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.07543829680688541</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.377594798997925</v>
+        <v>0.6842575565833596</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.5881881713867188</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.377594854348478</v>
+        <v>0.6842576119339135</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.25054532289505</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.377594999643682</v>
+        <v>0.6842577572291174</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4403733313083649</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5852000093893223</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.377594965049586</v>
+        <v>0.6842577226350212</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.2418403476476669</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.377594951211948</v>
+        <v>0.6842577087973827</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.8907974362373352</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.377595041156598</v>
+        <v>0.6842577987420329</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.7502635717391968</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7360766030030931</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.377595359422282</v>
+        <v>0.6842581170077174</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.1135056987404823</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.07543829680688541</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.377595179532982</v>
+        <v>0.6842579371184173</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.2120379954576492</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5852000093893223</v>
+        <v>0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.377595221045898</v>
+        <v>0.6842579786313328</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4939952790737152</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.377595034237779</v>
+        <v>0.6842577918232134</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.1489765793085098</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.377595103425971</v>
+        <v>0.684257861011406</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3572872877120972</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7852000093893223</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.377594902780213</v>
+        <v>0.6842576603656481</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3922038376331329</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1245617031931146</v>
+        <v>0.72</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.377594944293129</v>
+        <v>0.6842577018785635</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.5372811555862427</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.2057574499049892</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.377594971968406</v>
+        <v>0.6842577295538403</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_4_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_4_000006.xlsx
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.3828900456428528</v>
+        <v>0.3828900754451752</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.4399999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.450840562582016</v>
+        <v>0.4508405029773712</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.4399999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.4089353084564209</v>
+        <v>0.4089352786540985</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.4464789927005768</v>
+        <v>0.4464789032936096</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.7199999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.4157023727893829</v>
+        <v>0.4157023429870605</v>
       </c>
       <c r="JB30" t="n">
         <v>0.4399999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.4903578758239746</v>
+        <v>0.4903578162193298</v>
       </c>
       <c r="JB41" t="n">
         <v>0.3</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.1698305755853653</v>
+        <v>0.1698306202888489</v>
       </c>
       <c r="JB46" t="n">
         <v>0.3</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.8114120364189148</v>
+        <v>0.8114120960235596</v>
       </c>
       <c r="JB50" t="n">
         <v>0.3</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.4325738847255707</v>
+        <v>0.4325738549232483</v>
       </c>
       <c r="JB52" t="n">
         <v>0.7199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.8668186664581299</v>
+        <v>0.8668185472488403</v>
       </c>
       <c r="JB54" t="n">
         <v>0.4399999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.02854069508612156</v>
+        <v>0.02854070067405701</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.7199999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.293013870716095</v>
+        <v>0.2930139303207397</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.2160382568836212</v>
+        <v>0.2160382121801376</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.1359606236219406</v>
+        <v>0.1359606832265854</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.1600000000000001</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.09057268500328064</v>
+        <v>0.09057272970676422</v>
       </c>
       <c r="JB71" t="n">
         <v>0.16</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.03805523365736008</v>
+        <v>0.03805526718497276</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.2162179499864578</v>
+        <v>0.2162179946899414</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.4318846464157104</v>
+        <v>0.4318847060203552</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.2142759412527084</v>
+        <v>0.2142759710550308</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.7199999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.2361670881509781</v>
+        <v>0.2361671477556229</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.235644742846489</v>
+        <v>0.2356447726488113</v>
       </c>
       <c r="JB86" t="n">
         <v>0.16</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.3782603740692139</v>
+        <v>0.3782604336738586</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.7199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.811101496219635</v>
+        <v>0.8111013174057007</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.7199999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.2352587431669235</v>
+        <v>0.2352588027715683</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.1436575204133987</v>
+        <v>0.1436575502157211</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.7199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.08840598911046982</v>
+        <v>0.08840600401163101</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.5799999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.1922974437475204</v>
+        <v>0.1922974139451981</v>
       </c>
       <c r="JB95" t="n">
         <v>0.16</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.6023468971252441</v>
+        <v>0.6023467779159546</v>
       </c>
       <c r="JB97" t="n">
         <v>0.1600000000000001</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.3031907975673676</v>
+        <v>0.3031908273696899</v>
       </c>
       <c r="JB98" t="n">
         <v>0.16</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.3287970125675201</v>
+        <v>0.3287970423698425</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.0459986999630928</v>
+        <v>0.045998714864254</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.3319389522075653</v>
+        <v>0.3319388926029205</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.7199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.6512879729270935</v>
+        <v>0.6512879133224487</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.7199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.08453602343797684</v>
+        <v>0.08453604578971863</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.7199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.2063437700271606</v>
+        <v>0.2063437551259995</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.4637946784496307</v>
+        <v>0.463794618844986</v>
       </c>
       <c r="JB109" t="n">
         <v>0.1600000000000001</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.2677534818649292</v>
+        <v>0.2677534222602844</v>
       </c>
       <c r="JB111" t="n">
         <v>0.16</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.5881881713867188</v>
+        <v>0.588188111782074</v>
       </c>
       <c r="JB114" t="n">
         <v>0.1600000000000001</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.2418403476476669</v>
+        <v>0.2418403327465057</v>
       </c>
       <c r="JB117" t="n">
         <v>0.4399999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.4939952790737152</v>
+        <v>0.4939952194690704</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.5799999999999998</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.5372811555862427</v>
+        <v>0.5372810959815979</v>
       </c>
       <c r="JB126" t="n">
         <v>0.8599999999999999</v>
